--- a/data/trans_camb/P16A08-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P16A08-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 3,0</t>
+          <t>-2,45; 2,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 1,91</t>
+          <t>-3,12; 2,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 2,21</t>
+          <t>-3,36; 2,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,19; 6,45</t>
+          <t>-0,05; 6,19</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 5,36</t>
+          <t>-0,69; 5,47</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,29; 5,51</t>
+          <t>0,37; 5,61</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 3,46</t>
+          <t>-0,59; 3,29</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 2,51</t>
+          <t>-1,35; 2,61</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 2,69</t>
+          <t>-1,08; 2,77</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-47,15; 123,68</t>
+          <t>-48,79; 116,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-64,76; 72,04</t>
+          <t>-59,61; 86,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-64,98; 91,45</t>
+          <t>-63,92; 88,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-9,0; 465,74</t>
+          <t>-8,62; 443,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-25,49; 391,56</t>
+          <t>-27,29; 368,05</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 417,72</t>
+          <t>0,42; 429,15</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-12,17; 135,14</t>
+          <t>-13,89; 132,22</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-31,79; 96,43</t>
+          <t>-31,96; 102,36</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-29,98; 108,56</t>
+          <t>-25,0; 106,87</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,94; 7,13</t>
+          <t>1,98; 7,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,24; 5,55</t>
+          <t>1,25; 5,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,11; 5,05</t>
+          <t>1,17; 5,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 4,07</t>
+          <t>-3,77; 4,05</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 2,49</t>
+          <t>-4,76; 2,44</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 3,97</t>
+          <t>-2,75; 4,36</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 4,2</t>
+          <t>-0,45; 4,43</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 3,01</t>
+          <t>-1,2; 3,27</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 3,48</t>
+          <t>-0,59; 3,71</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>78,03; —</t>
+          <t>84,68; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,03; —</t>
+          <t>28,9; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14,09; —</t>
+          <t>17,64; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-42,93; 89,42</t>
+          <t>-42,3; 85,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-56,5; 50,5</t>
+          <t>-54,46; 50,43</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-37,18; 81,82</t>
+          <t>-31,52; 91,95</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-9,42; 152,85</t>
+          <t>-11,07; 167,62</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-27,48; 107,21</t>
+          <t>-26,03; 133,28</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-17,49; 131,26</t>
+          <t>-14,78; 145,04</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 2,66</t>
+          <t>-1,28; 2,86</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 1,78</t>
+          <t>-2,2; 1,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 2,64</t>
+          <t>-2,88; 3,04</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 6,51</t>
+          <t>-0,19; 6,75</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,28; 11,7</t>
+          <t>2,27; 11,74</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,4; 6,99</t>
+          <t>0,47; 7,2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 3,26</t>
+          <t>-0,42; 3,1</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 3,35</t>
+          <t>-0,53; 3,32</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 3,07</t>
+          <t>-1,95; 3,1</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-44,39; 152,25</t>
+          <t>-38,55; 181,46</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-63,33; 101,41</t>
+          <t>-61,08; 124,01</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-71,88; 124,68</t>
+          <t>-73,25; 140,86</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-22,91; 1138,45</t>
+          <t>-35,1; 1035,35</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>25,96; 2014,57</t>
+          <t>27,06; 1855,86</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-15,74; 1181,62</t>
+          <t>-5,13; 1264,75</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-23,66; 191,04</t>
+          <t>-16,85; 171,03</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-17,62; 193,02</t>
+          <t>-22,54; 193,33</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-52,87; 159,22</t>
+          <t>-49,6; 168,75</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 1,27</t>
+          <t>-1,29; 1,4</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 1,26</t>
+          <t>-1,26; 1,33</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 2,04</t>
+          <t>-0,87; 2,02</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,83; 5,53</t>
+          <t>0,71; 5,44</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 3,97</t>
+          <t>-0,4; 4,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 1,4</t>
+          <t>-3,08; 1,42</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,07; 2,66</t>
+          <t>0,11; 2,57</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 2,28</t>
+          <t>-0,27; 2,08</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 1,38</t>
+          <t>-1,17; 1,34</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-42,67; 73,0</t>
+          <t>-42,45; 80,05</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-43,67; 71,31</t>
+          <t>-42,64; 77,73</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-33,75; 110,82</t>
+          <t>-31,25; 111,6</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13,14; 170,38</t>
+          <t>9,82; 166,33</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-12,08; 119,01</t>
+          <t>-8,05; 121,83</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-57,63; 37,97</t>
+          <t>-59,99; 41,87</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,82; 106,62</t>
+          <t>1,97; 104,3</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-8,22; 93,63</t>
+          <t>-7,31; 84,57</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-29,58; 52,54</t>
+          <t>-32,91; 55,27</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 3,39</t>
+          <t>-0,86; 3,41</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 3,61</t>
+          <t>-0,37; 3,51</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,02; 4,7</t>
+          <t>-0,17; 4,59</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 2,74</t>
+          <t>-1,5; 2,75</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 4,16</t>
+          <t>-0,59; 4,02</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 32,51</t>
+          <t>-0,19; 31,23</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 2,34</t>
+          <t>-0,6; 2,29</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 3,04</t>
+          <t>0,08; 3,18</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,61; 23,68</t>
+          <t>0,75; 20,68</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-36,6; 466,94</t>
+          <t>-39,9; 418,26</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-27,6; 450,12</t>
+          <t>-24,88; 449,82</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-13,16; 530,2</t>
+          <t>-14,74; 591,81</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-33,11; 127,01</t>
+          <t>-35,34; 118,27</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-11,11; 177,59</t>
+          <t>-13,92; 170,5</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 1396,35</t>
+          <t>-6,33; 1449,05</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-21,0; 121,22</t>
+          <t>-20,6; 116,95</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 155,91</t>
+          <t>0,59; 164,91</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>20,41; 981,4</t>
+          <t>24,59; 1076,94</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,41; 7,19</t>
+          <t>0,09; 7,26</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 5,55</t>
+          <t>-0,53; 5,9</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 8,34</t>
+          <t>-1,64; 9,12</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 3,0</t>
+          <t>-0,49; 2,85</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 2,75</t>
+          <t>-0,75; 2,74</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 1,78</t>
+          <t>-1,52; 1,64</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,17; 3,22</t>
+          <t>0,21; 3,29</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 2,74</t>
+          <t>-0,25; 2,8</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 2,29</t>
+          <t>-1,15; 2,25</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>3,79; 649,88</t>
+          <t>-5,27; 466,01</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-25,73; 458,66</t>
+          <t>-25,79; 432,17</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-67,7; 633,93</t>
+          <t>-63,94; 665,78</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-10,52; 95,9</t>
+          <t>-11,35; 93,07</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-17,86; 84,26</t>
+          <t>-18,77; 84,43</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-35,97; 60,31</t>
+          <t>-36,77; 52,83</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>3,31; 112,16</t>
+          <t>4,8; 119,07</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 93,91</t>
+          <t>-7,45; 95,4</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-31,37; 76,43</t>
+          <t>-29,33; 80,23</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,94</t>
+          <t>0,13; 1,93</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 1,52</t>
+          <t>-0,15; 1,55</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 1,76</t>
+          <t>-0,21; 1,89</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,72</t>
+          <t>0,68; 2,6</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,44</t>
+          <t>0,47; 2,46</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,12; 8,95</t>
+          <t>0,1; 8,87</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,62; 1,91</t>
+          <t>0,66; 2,04</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,68</t>
+          <t>0,4; 1,81</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,41; 6,5</t>
+          <t>0,37; 5,6</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>5,82; 94,99</t>
+          <t>3,93; 94,6</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 74,68</t>
+          <t>-5,8; 74,75</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 85,89</t>
+          <t>-8,16; 90,04</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>13,11; 78,07</t>
+          <t>14,64; 76,17</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>7,3; 69,81</t>
+          <t>10,58; 70,43</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,58; 231,23</t>
+          <t>1,64; 227,15</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>17,31; 67,58</t>
+          <t>18,64; 73,98</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>11,46; 57,85</t>
+          <t>11,46; 65,31</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>11,95; 191,1</t>
+          <t>9,74; 167,9</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A08-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P16A08-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-0,76</t>
+          <t>-0,93</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,96</t>
+          <t>3,0</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,87</t>
+          <t>0,8</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 2,94</t>
+          <t>-2,55; 2,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 2,24</t>
+          <t>-3,15; 2,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 2,15</t>
+          <t>-3,59; 1,67</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 6,19</t>
+          <t>0,18; 6,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 5,47</t>
+          <t>-0,57; 5,12</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,37; 5,61</t>
+          <t>0,4; 5,6</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 3,29</t>
+          <t>-0,77; 3,35</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 2,61</t>
+          <t>-1,55; 2,49</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 2,77</t>
+          <t>-1,18; 2,7</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-18,79%</t>
+          <t>-23,07%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>116,1%</t>
+          <t>117,73%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>23,29%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-48,79; 116,18</t>
+          <t>-48,95; 107,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-59,61; 86,42</t>
+          <t>-57,16; 82,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-63,92; 88,65</t>
+          <t>-65,6; 63,41</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-8,62; 443,86</t>
+          <t>-2,76; 422,59</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-27,29; 368,05</t>
+          <t>-20,19; 398,17</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,42; 429,15</t>
+          <t>2,74; 458,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-13,89; 132,22</t>
+          <t>-17,99; 130,38</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-31,96; 102,36</t>
+          <t>-37,13; 95,64</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-25,0; 106,87</t>
+          <t>-26,39; 101,59</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,77</t>
+          <t>2,78</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,62</t>
+          <t>0,67</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,5</t>
+          <t>1,57</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,98; 7,12</t>
+          <t>1,96; 6,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,25; 5,51</t>
+          <t>1,18; 5,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,17; 5,17</t>
+          <t>1,29; 5,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 4,05</t>
+          <t>-3,63; 4,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 2,44</t>
+          <t>-5,16; 2,4</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 4,36</t>
+          <t>-2,78; 4,09</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 4,43</t>
+          <t>-0,33; 4,38</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 3,27</t>
+          <t>-1,3; 3,03</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 3,71</t>
+          <t>-0,49; 3,46</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>507,72%</t>
+          <t>508,67%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>42,24%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>84,68; —</t>
+          <t>58,88; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>28,9; —</t>
+          <t>9,23; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17,64; —</t>
+          <t>18,67; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-42,3; 85,04</t>
+          <t>-43,43; 95,96</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-54,46; 50,43</t>
+          <t>-56,54; 53,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-31,52; 91,95</t>
+          <t>-31,53; 88,7</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-11,07; 167,62</t>
+          <t>-8,74; 160,4</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-26,03; 133,28</t>
+          <t>-27,1; 110,15</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-14,78; 145,04</t>
+          <t>-11,09; 132,23</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,14</t>
+          <t>1,69</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,61</t>
+          <t>3,71</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,86</t>
+          <t>2,22</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 2,86</t>
+          <t>-1,6; 2,68</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 1,79</t>
+          <t>-2,15; 1,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 3,04</t>
+          <t>-0,62; 4,23</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 6,75</t>
+          <t>0,18; 6,96</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,27; 11,74</t>
+          <t>1,98; 12,13</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,47; 7,2</t>
+          <t>0,39; 7,46</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 3,1</t>
+          <t>-0,42; 3,24</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 3,32</t>
+          <t>-0,47; 3,37</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 3,1</t>
+          <t>0,21; 4,3</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>63,34%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>200,4%</t>
+          <t>205,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>90,24%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-38,55; 181,46</t>
+          <t>-45,96; 150,86</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-61,08; 124,01</t>
+          <t>-63,04; 120,07</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-73,25; 140,86</t>
+          <t>-22,26; 241,59</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-35,1; 1035,35</t>
+          <t>-19,51; 1213,58</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>27,06; 1855,86</t>
+          <t>2,83; 1646,7</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 1264,75</t>
+          <t>-8,72; 1194,79</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-16,85; 171,03</t>
+          <t>-19,32; 195,8</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-22,54; 193,33</t>
+          <t>-17,45; 203,22</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-49,6; 168,75</t>
+          <t>1,7; 250,12</t>
         </is>
       </c>
     </row>
@@ -1282,24 +1282,24 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>0,69</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3,03</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,85</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>0,45</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3,03</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1,85</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-0,53</t>
-        </is>
-      </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
           <t>1,26</t>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,19</t>
+          <t>0,7</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 1,4</t>
+          <t>-1,38; 1,37</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 1,33</t>
+          <t>-1,45; 1,19</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 2,02</t>
+          <t>-0,87; 2,04</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,71; 5,44</t>
+          <t>0,77; 5,71</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 4,0</t>
+          <t>-0,4; 4,19</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 1,42</t>
+          <t>-1,49; 2,36</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,11; 2,57</t>
+          <t>0,05; 2,48</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 2,08</t>
+          <t>-0,34; 2,1</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 1,34</t>
+          <t>-0,48; 1,83</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-12,76%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>23,09%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-42,45; 80,05</t>
+          <t>-44,77; 77,46</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-42,64; 77,73</t>
+          <t>-46,18; 71,2</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-31,25; 111,6</t>
+          <t>-29,84; 116,11</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9,82; 166,33</t>
+          <t>14,9; 179,7</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-8,05; 121,83</t>
+          <t>-10,1; 128,53</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-59,99; 41,87</t>
+          <t>-28,54; 81,79</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,97; 104,3</t>
+          <t>0,41; 97,63</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-7,31; 84,57</t>
+          <t>-9,67; 86,21</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-32,91; 55,27</t>
+          <t>-13,32; 73,35</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2,3</t>
+          <t>1,75</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,38</t>
+          <t>1,28</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>6,22</t>
+          <t>1,43</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 3,41</t>
+          <t>-0,98; 3,22</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 3,51</t>
+          <t>-0,28; 3,44</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 4,59</t>
+          <t>-0,28; 3,73</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 2,75</t>
+          <t>-1,64; 2,83</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 4,02</t>
+          <t>-0,49; 3,85</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 31,23</t>
+          <t>-0,88; 3,17</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 2,29</t>
+          <t>-0,73; 2,28</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,08; 3,18</t>
+          <t>-0,01; 3,23</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,75; 20,68</t>
+          <t>-0,24; 2,83</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>137,6%</t>
+          <t>104,96%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>245,61%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>226,3%</t>
+          <t>51,83%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-39,9; 418,26</t>
+          <t>-42,46; 353,7</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-24,88; 449,82</t>
+          <t>-21,54; 451,34</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-14,74; 591,81</t>
+          <t>-18,45; 438,52</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-35,34; 118,27</t>
+          <t>-35,05; 133,62</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-13,92; 170,5</t>
+          <t>-11,93; 174,89</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 1449,05</t>
+          <t>-21,61; 140,67</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-20,6; 116,95</t>
+          <t>-20,5; 123,26</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>0,59; 164,91</t>
+          <t>-1,63; 170,55</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>24,59; 1076,94</t>
+          <t>-6,93; 149,28</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1,69</t>
+          <t>0,74</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-0,1</t>
+          <t>0,02</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,27</t>
+          <t>0,14</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,09; 7,26</t>
+          <t>0,48; 7,39</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 5,9</t>
+          <t>-0,4; 5,77</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 9,12</t>
+          <t>-2,12; 4,69</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 2,85</t>
+          <t>-0,51; 3,13</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 2,74</t>
+          <t>-0,75; 2,88</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 1,64</t>
+          <t>-1,62; 1,77</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,21; 3,29</t>
+          <t>0,19; 3,17</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 2,8</t>
+          <t>-0,32; 2,64</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 2,25</t>
+          <t>-1,26; 1,89</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>70,13%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-2,59%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>4,11%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-5,27; 466,01</t>
+          <t>3,01; 539,11</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-25,79; 432,17</t>
+          <t>-21,35; 389,48</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-63,94; 665,78</t>
+          <t>-74,22; 374,39</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-11,35; 93,07</t>
+          <t>-12,51; 100,55</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-18,77; 84,43</t>
+          <t>-17,43; 94,25</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-36,77; 52,83</t>
+          <t>-36,54; 55,08</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>4,8; 119,07</t>
+          <t>3,83; 112,2</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-7,45; 95,4</t>
+          <t>-7,45; 94,01</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-29,33; 80,23</t>
+          <t>-31,94; 64,22</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>0,82</t>
+          <t>0,96</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,37</t>
+          <t>1,03</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1,63</t>
+          <t>1,01</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,93</t>
+          <t>0,1; 1,92</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 1,55</t>
+          <t>-0,15; 1,5</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 1,89</t>
+          <t>0,12; 1,89</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,6</t>
+          <t>0,67; 2,7</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,47; 2,46</t>
+          <t>0,43; 2,55</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,1; 8,87</t>
+          <t>0,07; 1,96</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,66; 2,04</t>
+          <t>0,67; 1,98</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,81</t>
+          <t>0,44; 1,71</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,37; 5,6</t>
+          <t>0,34; 1,58</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>40,21%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>60,48%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>51,32%</t>
+          <t>31,75%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>3,93; 94,6</t>
+          <t>2,87; 92,75</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-5,8; 74,75</t>
+          <t>-5,87; 76,83</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-8,16; 90,04</t>
+          <t>2,05; 91,84</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>14,64; 76,17</t>
+          <t>14,09; 78,46</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>10,58; 70,43</t>
+          <t>11,34; 74,67</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,64; 227,15</t>
+          <t>1,15; 56,35</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>18,64; 73,98</t>
+          <t>19,33; 69,22</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>11,46; 65,31</t>
+          <t>13,15; 59,19</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>9,74; 167,9</t>
+          <t>10,12; 56,84</t>
         </is>
       </c>
     </row>
